--- a/ope勤務条件表_2026.xlsx
+++ b/ope勤務条件表_2026.xlsx
@@ -10,6 +10,7 @@
     <sheet name="スタッフマスタ" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="シフト制約条件" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="手術スケジュール" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="設定" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -511,16 +512,11 @@
           <t>週5日</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
           <t>通常</t>
@@ -556,16 +552,11 @@
           <t>週5日</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
           <t>通常</t>
@@ -601,20 +592,16 @@
           <t>週5日</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr">
         <is>
           <t>月曜出勤必須</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
           <t>通常</t>
@@ -650,20 +637,16 @@
           <t>週5日</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
           <t>月曜出勤必須</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
           <t>通常</t>
@@ -699,16 +682,11 @@
           <t>週5日</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
           <t>通常</t>
@@ -754,10 +732,6 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>通常</t>
@@ -793,16 +767,11 @@
           <t>週5日</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>通常</t>
@@ -848,10 +817,6 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
           <t>通常</t>
@@ -902,8 +867,6 @@
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>17:30</t>
@@ -944,14 +907,11 @@
           <t>週5日</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>9:00</t>
@@ -997,16 +957,11 @@
           <t>除外</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
           <t>通常</t>
@@ -1052,10 +1007,6 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
           <t>時短</t>
@@ -1091,16 +1042,11 @@
           <t>週5日</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
           <t>通常</t>
@@ -1136,16 +1082,11 @@
           <t>週4日（必要に応じて週5日可）</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
           <t>通常</t>
@@ -1181,16 +1122,11 @@
           <t>週4日</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
           <t>通常</t>
@@ -1236,10 +1172,6 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
           <t>通常</t>
@@ -1285,14 +1217,11 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
       <c r="I18" t="inlineStr">
         <is>
           <t>火・水・木</t>
         </is>
       </c>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
           <t>通常</t>
@@ -1338,14 +1267,11 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
       <c r="I19" t="inlineStr">
         <is>
           <t>月・金・土</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
           <t>通常</t>
@@ -1381,16 +1307,11 @@
           <t>週5日</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
           <t>通常</t>
@@ -1436,8 +1357,6 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>8:30</t>
@@ -1483,16 +1402,11 @@
           <t>週5日</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
           <t>通常</t>
@@ -1528,16 +1442,11 @@
           <t>週5日</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr"/>
       <c r="G23" t="inlineStr">
         <is>
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
           <t>時短</t>
@@ -1573,16 +1482,11 @@
           <t>週5日</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr"/>
       <c r="G24" t="inlineStr">
         <is>
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
           <t>通常</t>
@@ -1618,16 +1522,11 @@
           <t>週5日</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr"/>
       <c r="G25" t="inlineStr">
         <is>
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
           <t>通常</t>
@@ -1673,9 +1572,6 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>17:30</t>
@@ -1726,14 +1622,11 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
       <c r="I27" t="inlineStr">
         <is>
           <t>月・木・金</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
           <t>通常</t>
@@ -1818,7 +1711,6 @@
       <c r="E2" t="n">
         <v>1</v>
       </c>
-      <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
           <t>HARD</t>
@@ -1849,7 +1741,6 @@
       <c r="E3" t="n">
         <v>2</v>
       </c>
-      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>HARD</t>
@@ -1880,7 +1771,6 @@
       <c r="E4" t="n">
         <v>1</v>
       </c>
-      <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr">
         <is>
           <t>HARD</t>
@@ -1911,7 +1801,6 @@
       <c r="E5" t="n">
         <v>1</v>
       </c>
-      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>HARD</t>
@@ -1942,7 +1831,6 @@
       <c r="E6" t="n">
         <v>1</v>
       </c>
-      <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr">
         <is>
           <t>HARD</t>
@@ -1973,7 +1861,6 @@
       <c r="E7" t="n">
         <v>1</v>
       </c>
-      <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr">
         <is>
           <t>HARD</t>
@@ -2004,7 +1891,6 @@
       <c r="E8" t="n">
         <v>2</v>
       </c>
-      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>HARD</t>
@@ -2134,7 +2020,6 @@
       <c r="E12" t="n">
         <v>0</v>
       </c>
-      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
           <t>HARD</t>
@@ -2198,7 +2083,6 @@
       <c r="E14" t="n">
         <v>1</v>
       </c>
-      <c r="F14" t="inlineStr"/>
       <c r="G14" t="inlineStr">
         <is>
           <t>HARD</t>
@@ -2257,7 +2141,6 @@
           <t>重城</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2275,7 +2158,6 @@
           <t>恩田</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -2293,7 +2175,6 @@
           <t>恩田</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -2311,7 +2192,6 @@
           <t>恩田</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2329,7 +2209,6 @@
           <t>相原</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -2347,7 +2226,6 @@
           <t>宮田</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -2365,7 +2243,6 @@
           <t>真下</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -2405,7 +2282,6 @@
           <t>恩田</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -2423,7 +2299,6 @@
           <t>重城</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -2441,7 +2316,6 @@
           <t>恩田</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2459,7 +2333,6 @@
           <t>真下</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2477,7 +2350,6 @@
           <t>恩田</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2517,7 +2389,6 @@
           <t>恩田</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2535,7 +2406,6 @@
           <t>恩田</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2553,7 +2423,6 @@
           <t>恩田</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2571,7 +2440,6 @@
           <t>恩田</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2611,7 +2479,6 @@
           <t>恩田</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2629,7 +2496,6 @@
           <t>恩田</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2647,7 +2513,6 @@
           <t>真下</t>
         </is>
       </c>
-      <c r="D23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2665,7 +2530,292 @@
           <t>恩田</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="45" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>設定項目</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>設定値</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>初期値</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>単位/選択肢</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>説明</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>2階裏_基本人数</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>3</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>名</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>2階裏の基本出勤人数（有休時はここから減算）</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>2階裏_看護師最低人数</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>名</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>2階裏で絶対に欠かせない看護師の最低人数 (HARD制約)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2階裏_看護師推奨人数</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>2</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>名</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>2階裏で理想とされる看護師の人数 (不足時ソフトペナルティ)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>連勤上限日数</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>5</v>
+      </c>
+      <c r="C5" t="n">
+        <v>5</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>連続勤務の上限日数（5なら6連勤を禁止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>固定公休_削減許容日数</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>カレンダー物理不足時の固定公休者の削減下限 (目標-N日)</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>3連休抑制レベル</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>強 / 中 / 弱 / なし</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>有休を除く通常の3連休発生を抑える強さ</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>セクション人数ブレ幅</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1</v>
+      </c>
+      <c r="C8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>名</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>各セクションの平均出勤人数からの許容範囲 (平均±N名)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>週休配分目標</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>7日間ローリング期間中の公休目標日数 (週休2日平準化の基準)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>既存シフト維持レベル</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>中</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>強 / 中 / 弱</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>前回の生成結果がある場合の維持の強さ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2階裏_警告表示人数</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>名以下</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Excel出力時に警告マーク(⚠️)を付ける2階裏の出勤人数</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/ope勤務条件表_2026.xlsx
+++ b/ope勤務条件表_2026.xlsx
@@ -2542,7 +2542,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2817,6 +2817,110 @@
         </is>
       </c>
     </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>祝日週_公休設定</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>有効</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>有効</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>有効 / 無効</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>祝日により診療日が5日となる週に最低1日の公休を設定（5連勤防止）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>週単位_公休平準化</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>有効</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>有効</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>有効 / 無効</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>各週の公休日数を勤務パターンに応じて平準化（週4は週2日、週5は週1日）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2階裏_週4名最低日数</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" t="n">
+        <v>2</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>日</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>2階裏の通常週(6日間)における4名出勤の最低確保日数</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>空欄公休ローテーション</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>有効</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>有効</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>有効 / 無効</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>希望公休が空欄のスタッフに平日主公休を設定し月替わりでローテーション</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/ope勤務条件表_2026.xlsx
+++ b/ope勤務条件表_2026.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M27"/>
+  <dimension ref="A1:N27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,25 +462,30 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>指定公休日</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>希望出勤曜日</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>勤務開始時刻</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>勤務終了時刻</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="M1" t="inlineStr">
         <is>
           <t>勤務タイプ</t>
         </is>
       </c>
-      <c r="M1" t="inlineStr">
+      <c r="N1" t="inlineStr">
         <is>
           <t>除外フラグ</t>
         </is>
@@ -517,12 +522,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M2" t="b">
+      <c r="N2" t="b">
         <v>0</v>
       </c>
     </row>
@@ -557,12 +562,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M3" t="b">
+      <c r="N3" t="b">
         <v>0</v>
       </c>
     </row>
@@ -597,17 +602,17 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="J4" t="inlineStr">
         <is>
           <t>月曜出勤必須</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M4" t="b">
+      <c r="N4" t="b">
         <v>0</v>
       </c>
     </row>
@@ -642,17 +647,17 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="J5" t="inlineStr">
         <is>
           <t>月曜出勤必須</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M5" t="b">
+      <c r="N5" t="b">
         <v>0</v>
       </c>
     </row>
@@ -687,12 +692,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M6" t="b">
+      <c r="N6" t="b">
         <v>0</v>
       </c>
     </row>
@@ -732,12 +737,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M7" t="b">
+      <c r="N7" t="b">
         <v>0</v>
       </c>
     </row>
@@ -772,12 +777,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M8" t="b">
+      <c r="N8" t="b">
         <v>0</v>
       </c>
     </row>
@@ -817,12 +822,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M9" t="b">
+      <c r="N9" t="b">
         <v>0</v>
       </c>
     </row>
@@ -867,17 +872,17 @@
           <t>2026-11-10</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="M10" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M10" t="b">
+      <c r="N10" t="b">
         <v>0</v>
       </c>
     </row>
@@ -912,22 +917,22 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr">
+      <c r="K11" t="inlineStr">
         <is>
           <t>9:00</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>17:00</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M11" t="b">
+      <c r="N11" t="b">
         <v>0</v>
       </c>
     </row>
@@ -962,12 +967,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M12" t="b">
+      <c r="N12" t="b">
         <v>1</v>
       </c>
     </row>
@@ -1007,12 +1012,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
+      <c r="M13" t="inlineStr">
         <is>
           <t>時短</t>
         </is>
       </c>
-      <c r="M13" t="b">
+      <c r="N13" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1047,12 +1052,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
+      <c r="M14" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M14" t="b">
+      <c r="N14" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1087,12 +1092,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M15" t="b">
+      <c r="N15" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1127,12 +1132,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
+      <c r="M16" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M16" t="b">
+      <c r="N16" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1172,12 +1177,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M17" t="b">
+      <c r="N17" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1217,17 +1222,17 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>火・水・木</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
+      <c r="M18" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M18" t="b">
+      <c r="N18" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1267,17 +1272,17 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="I19" t="inlineStr">
+      <c r="J19" t="inlineStr">
         <is>
           <t>月・金・土</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M19" t="b">
+      <c r="N19" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1312,12 +1317,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M20" t="b">
+      <c r="N20" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1357,22 +1362,22 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>8:30</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>18:00</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M21" t="b">
+      <c r="N21" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1407,12 +1412,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
+      <c r="M22" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M22" t="b">
+      <c r="N22" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1447,12 +1452,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>時短</t>
         </is>
       </c>
-      <c r="M23" t="b">
+      <c r="N23" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1487,12 +1492,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M24" t="b">
+      <c r="N24" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1527,12 +1532,12 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
+      <c r="M25" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M25" t="b">
+      <c r="N25" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1572,17 +1577,17 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>17:30</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M26" t="b">
+      <c r="N26" t="b">
         <v>0</v>
       </c>
     </row>
@@ -1622,17 +1627,17 @@
           <t>2026/12/29-2027/01/03</t>
         </is>
       </c>
-      <c r="I27" t="inlineStr">
+      <c r="J27" t="inlineStr">
         <is>
           <t>月・木・金</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>通常</t>
         </is>
       </c>
-      <c r="M27" t="b">
+      <c r="N27" t="b">
         <v>0</v>
       </c>
     </row>
@@ -2542,7 +2547,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2921,6 +2926,33 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>指定公休日_有効</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>有効</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>有効</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>有効 / 無効</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>スタッフマスタの指定公休日をHARD制約として強制適用</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
